--- a/data/trans_dic/P19C10_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19C10_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por dolor de mandíbula / solo 2023</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por dolor de mandíbula / solo 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,99</t>
+          <t>0,0; 1,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,37</t>
+          <t>0,0; 0,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,59</t>
+          <t>0,03; 0,64</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,78</t>
+          <t>0,0; 0,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,33</t>
+          <t>0,31; 1,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,8</t>
+          <t>0,21; 0,77</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,75</t>
+          <t>0,17; 1,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,02</t>
+          <t>0,14; 1,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,06</t>
+          <t>0,27; 1,12</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,4</t>
+          <t>0,39; 1,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,87</t>
+          <t>0,29; 0,91</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,57</t>
+          <t>0,15; 0,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,82</t>
+          <t>0,38; 0,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,62</t>
+          <t>0,31; 0,6</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por dolor de mandíbula / solo 2023</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por dolor de mandíbula / solo 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6030</t>
+          <t>0; 7470</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2406</t>
+          <t>0; 2540</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>356; 7465</t>
+          <t>347; 8144</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 9152</t>
+          <t>0; 10110</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3163; 12525</t>
+          <t>2959; 11644</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4222; 16857</t>
+          <t>4447; 16215</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1195; 12004</t>
+          <t>1184; 12680</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1300; 9398</t>
+          <t>1249; 9219</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4033; 17022</t>
+          <t>4410; 18088</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6263</t>
+          <t>0; 6492</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4124; 14833</t>
+          <t>4137; 15128</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5669; 16976</t>
+          <t>5677; 17769</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4182; 18953</t>
+          <t>5032; 19801</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13197; 29381</t>
+          <t>13498; 28889</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20987; 42989</t>
+          <t>21345; 41908</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C10_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19C10_2023-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,39</t>
+          <t>0,0; 0,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,64</t>
+          <t>0,02; 0,52</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,87</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,24</t>
+          <t>0,38; 1,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,77</t>
+          <t>0,27; 0,96</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,85</t>
+          <t>0,16; 1,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,0</t>
+          <t>0,33; 1,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,12</t>
+          <t>0,37; 1,24</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,73</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,42</t>
+          <t>0,46; 1,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,91</t>
+          <t>0,29; 0,89</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,59</t>
+          <t>0,15; 0,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,81</t>
+          <t>0,43; 0,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,6</t>
+          <t>0,35; 0,66</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>686</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>1987</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 7470</t>
+          <t>0; 6424</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2540</t>
+          <t>0; 2331</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>347; 8144</t>
+          <t>338; 7057</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>2797</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8537</t>
+          <t>10401</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 10110</t>
+          <t>0; 12846</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2959; 11644</t>
+          <t>3998; 14263</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4447; 16215</t>
+          <t>5558; 19736</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5023</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4593</t>
+          <t>5718</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9616</t>
+          <t>10771</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1184; 12680</t>
+          <t>1218; 12325</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1249; 9219</t>
+          <t>2605; 10646</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4410; 18088</t>
+          <t>5801; 19495</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1567</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8394</t>
+          <t>8977</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9961</t>
+          <t>10580</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6492</t>
+          <t>0; 5945</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4137; 15128</t>
+          <t>4905; 16480</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5677; 17769</t>
+          <t>5779; 18066</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10277</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19862</t>
+          <t>22984</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30139</t>
+          <t>33739</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5032; 19801</t>
+          <t>5019; 20541</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13498; 28889</t>
+          <t>15731; 33037</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21345; 41908</t>
+          <t>24385; 46626</t>
         </is>
       </c>
     </row>
